--- a/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
@@ -18313,13 +18313,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B956A473-B99B-4061-B43B-90A8A4A92BCD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76763142-ACBF-476C-A337-B8D2006213CB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8374A36-00D7-4C01-B48B-62647459739C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B04AD5F-26D0-4CF1-9824-EE12D5555C04}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{539CE6E9-3929-4ED5-80CB-E091EFED865D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7274DE-7BEF-4764-A13F-22C0C93EF906}"/>
 </file>
--- a/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
@@ -18313,13 +18313,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76763142-ACBF-476C-A337-B8D2006213CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4D0962-1433-4406-B6B3-262C28965A83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B04AD5F-26D0-4CF1-9824-EE12D5555C04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53A175F6-E048-4ACC-BBC8-72941CF0603E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7274DE-7BEF-4764-A13F-22C0C93EF906}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0747CE8-C34C-4294-B855-53003445D952}"/>
 </file>
--- a/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
+++ b/ksoft_old/docs/records/Itinerarios_Control_Points_CD2567_Records.xlsx
@@ -18313,13 +18313,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4D0962-1433-4406-B6B3-262C28965A83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B956A473-B99B-4061-B43B-90A8A4A92BCD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53A175F6-E048-4ACC-BBC8-72941CF0603E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8374A36-00D7-4C01-B48B-62647459739C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0747CE8-C34C-4294-B855-53003445D952}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{539CE6E9-3929-4ED5-80CB-E091EFED865D}"/>
 </file>